--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Orientamento e formazione.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Orientamento e formazione.xlsx
@@ -147,7 +147,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi le iniziative</t>
+    <t>Cerca le iniziative</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -400,7 +400,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> della città. 
+      <t xml:space="preserve"> della città.
 </t>
     </r>
     <r>
@@ -418,7 +418,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -492,7 +492,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -520,7 +520,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Presenta richiesta</t>
+    <t>Invia richiesta</t>
   </si>
   <si>
     <r>
@@ -540,7 +540,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -598,8 +598,9 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
+    <t xml:space="preserve">✨Cosa puoi aggiungere:
+- Allegati: questa funzionalità permette di allegare documenti all'interno del messaggio.
+- Single Sign-on: l'utente può accedere al portale o all'area riservata dedicata premendo sul pulsante, senza doversi autenticare con SPID o CIE.</t>
   </si>
 </sst>
 </file>
